--- a/hardware/pcb/LED_board_iorodeo/assembly/BOM_JLCPCB_radial_16mA.xlsx
+++ b/hardware/pcb/LED_board_iorodeo/assembly/BOM_JLCPCB_radial_16mA.xlsx
@@ -1,17 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10731"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_1DDF5986B0FB2D9EA789C2EC9633963461924B3B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -20,204 +31,183 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
-  <si>
-    <t xml:space="preserve">Comment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Designator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Footprint</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>Footprint</t>
   </si>
   <si>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">LCSC Part #</t>
+      <t>LCSC Part #</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">（</t>
+      <t>（</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">optional</t>
+      <t>optional</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">）</t>
+      <t>）</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10V 10μF Ceramic Capacitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1,C2 C4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C315248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16V 100nF Ceramic Capacitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C60474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-Pin Connector, JST SM04B-SRSS-TB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J1 ,J2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMD,P=1mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C160404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7μH Inductor ±20%, 440mOhm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C114862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMBT5551LT1G Bipolar Transistor, 600mA NPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C41095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10Ω ±1%  Resistor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C854481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30kΩ ±1%  Resistor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C138008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1kΩ ±1%  Resistor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C144789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPS61222DCKR, boost converter, fixed 5V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-363-6(SC-70-6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C116461</t>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>10V 10μF Ceramic Capacitor</t>
+  </si>
+  <si>
+    <t>C1,C2 C4</t>
+  </si>
+  <si>
+    <t>0402</t>
+  </si>
+  <si>
+    <t>C315248</t>
+  </si>
+  <si>
+    <t>16V 100nF Ceramic Capacitor</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C60474</t>
+  </si>
+  <si>
+    <t>4-Pin Connector, JST SM04B-SRSS-TB</t>
+  </si>
+  <si>
+    <t>J1 ,J2</t>
+  </si>
+  <si>
+    <t>SMD,P=1mm</t>
+  </si>
+  <si>
+    <t>C160404</t>
+  </si>
+  <si>
+    <t>4.7μH Inductor ±20%, 440mOhm</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>0603</t>
+  </si>
+  <si>
+    <t>C114862</t>
+  </si>
+  <si>
+    <t>MMBT5551LT1G Bipolar Transistor, 600mA NPN</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>C41095</t>
+  </si>
+  <si>
+    <t>10Ω ±1%  Resistor</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>C854481</t>
+  </si>
+  <si>
+    <t>30kΩ ±1%  Resistor</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>C138008</t>
+  </si>
+  <si>
+    <t>1kΩ ±1%  Resistor</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>C144789</t>
+  </si>
+  <si>
+    <t>TPS61222DCKR, boost converter, fixed 5V</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>SOT-363-6(SC-70-6)</t>
+  </si>
+  <si>
+    <t>C116461</t>
   </si>
   <si>
     <t xml:space="preserve">LMV321 Operational Amplifier </t>
   </si>
   <si>
-    <t xml:space="preserve">U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-23-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C686637</t>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>SOT-23-5</t>
+  </si>
+  <si>
+    <t>C686637</t>
+  </si>
+  <si>
+    <t>PJSEMI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="0"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -227,7 +217,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -235,19 +225,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="134"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="0"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -272,88 +260,65 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -412,28 +377,356 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E1048576"/>
-  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AMJ11"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="27.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.89"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="6" style="3" width="8.89"/>
+    <col min="1" max="1" width="52.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.1328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.86328125" style="1"/>
+    <col min="6" max="1024" width="8.86328125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -450,7 +743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -463,11 +756,11 @@
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -480,11 +773,11 @@
       <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -497,11 +790,11 @@
       <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -514,11 +807,11 @@
       <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -531,11 +824,11 @@
       <c r="D6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -548,11 +841,11 @@
       <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -565,11 +858,11 @@
       <c r="D8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -582,11 +875,11 @@
       <c r="D9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
@@ -599,11 +892,11 @@
       <c r="D10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.1">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -616,26 +909,15 @@
       <c r="D11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="F11" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/hardware/pcb/LED_board_iorodeo/assembly/BOM_JLCPCB_radial_16mA.xlsx
+++ b/hardware/pcb/LED_board_iorodeo/assembly/BOM_JLCPCB_radial_16mA.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>Comment</t>
   </si>
@@ -197,12 +197,21 @@
   <si>
     <t>PJSEMI</t>
   </si>
+  <si>
+    <t>LMV321</t>
+  </si>
+  <si>
+    <t>C7972</t>
+  </si>
+  <si>
+    <t>vor 11 Stunden</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -237,6 +246,12 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="18"/>
     </font>
   </fonts>
   <fills count="4">
@@ -288,7 +303,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -312,6 +327,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -715,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ11"/>
+  <dimension ref="A1:AMJ12"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
     <col min="1" max="1" width="52.08984375" style="1" customWidth="1"/>
@@ -916,6 +934,23 @@
         <v>41</v>
       </c>
     </row>
+    <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.1">
+      <c r="A12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
